--- a/event_registration_forms/025_corporate_meeting_appointment_form--event_registration_forms.xlsx
+++ b/event_registration_forms/025_corporate_meeting_appointment_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'john',_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'John', 'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'jane',_'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Jane', 'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'joe',_'value':_'joe'}</t>
+          <t>joe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Joe', 'value': 'Joe'}</t>
+          <t>Joe</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'sales',_'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Sales', 'value': 'sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'marketing',_'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Marketing', 'value': 'marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'hr',_'value':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'HR', 'value': 'hr'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'monday',_'value':_1}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Monday', 'value': 1}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'tuesday',_'value':_2}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Tuesday', 'value': 2}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'wednesday',_'value':_3}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Wednesday', 'value': 3}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'thursday',_'value':_4}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Thursday', 'value': 4}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'friday',_'value':_5}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Friday', 'value': 5}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'morning',_'value':_1}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Morning', 'value': 1}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'afternoon',_'value':_2}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Afternoon', 'value': 2}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'evening',_'value':_3}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Evening', 'value': 3}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'weekends',_'value':_1}</t>
+          <t>weekends</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Weekends', 'value': 1}</t>
+          <t>Weekends</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'weekdays',_'value':_2}</t>
+          <t>weekdays</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Weekdays', 'value': 2}</t>
+          <t>Weekdays</t>
         </is>
       </c>
     </row>
